--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8869111-8A30-4F4C-A490-5294212C3E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35998551-C1B0-4733-80AA-F713941826F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1025,25 +1025,47 @@
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>350</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
+        <v>60</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35998551-C1B0-4733-80AA-F713941826F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6AB1C6-CC22-41BA-BC5E-F0C8E740E132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>CAP776 / D1P2636</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -1069,25 +1072,47 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>90</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6AB1C6-CC22-41BA-BC5E-F0C8E740E132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC458DE-5184-44CD-A2CF-FA5C2F5C8DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1116,25 +1116,47 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>150</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>90</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC458DE-5184-44CD-A2CF-FA5C2F5C8DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C65CF67-C70C-43EA-A28D-27A8A8C1DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1160,25 +1160,47 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>90</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C65CF67-C70C-43EA-A28D-27A8A8C1DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54F1E32-B21A-4DD7-A3D3-E1174F7AC7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1204,47 +1204,91 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>90</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>730</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>240</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>90</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54F1E32-B21A-4DD7-A3D3-E1174F7AC7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDF465D-AECE-4E1C-B55A-063F9FB644EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1292,25 +1292,47 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>180</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDF465D-AECE-4E1C-B55A-063F9FB644EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C76DCC4-36D2-429B-9DC6-0B5DF1DAF84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1336,25 +1336,47 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="14">
+        <v>350</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>90</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C76DCC4-36D2-429B-9DC6-0B5DF1DAF84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA06E38-9258-4336-A87A-60682DC9F130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1380,25 +1380,47 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA06E38-9258-4336-A87A-60682DC9F130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB64E37C-AD01-4D98-B86A-5B52690792B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1384,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B15" s="14">
         <v>420</v>
@@ -1424,113 +1427,223 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>580</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>580</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>240</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>90</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>300</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>180</v>
+      </c>
+      <c r="E20" s="14">
+        <v>45</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>485</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB64E37C-AD01-4D98-B86A-5B52690792B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62C55A2-A8C4-4CDF-AFCA-22030AB551AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1647,25 +1647,47 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>90</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62C55A2-A8C4-4CDF-AFCA-22030AB551AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458E83A7-435C-4B7F-89C6-5071D0F86A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1691,25 +1694,47 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>30</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458E83A7-435C-4B7F-89C6-5071D0F86A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F561DF-274D-4238-BD20-B1CA4BB61094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1738,25 +1738,47 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>30</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F561DF-274D-4238-BD20-B1CA4BB61094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5862E357-7C8B-4B13-A41F-C11D83FBB6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1782,113 +1782,223 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>30</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>20</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>760</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>20</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>20</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5862E357-7C8B-4B13-A41F-C11D83FBB6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A067CEBA-3FE0-4E5A-918C-16F05CF0B698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2002,25 +2002,47 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A067CEBA-3FE0-4E5A-918C-16F05CF0B698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE70D48-46E9-4F56-830E-5CE0B60D674C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2046,25 +2046,47 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE70D48-46E9-4F56-830E-5CE0B60D674C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB41D17-C1C2-4677-B4B0-21FEEE72BD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2090,91 +2090,179 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>240</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>90</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>240</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>90</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB41D17-C1C2-4677-B4B0-21FEEE72BD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D13C8C-687F-4A4D-8C36-2770EDAD8DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2266,25 +2266,47 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D13C8C-687F-4A4D-8C36-2770EDAD8DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF2A04F-9BDD-4FFC-8FA2-0273158245AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2310,25 +2310,47 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF2A04F-9BDD-4FFC-8FA2-0273158245AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C85B219-D7BD-40B5-8C2C-444A129EE394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2354,25 +2354,47 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>200</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C85B219-D7BD-40B5-8C2C-444A129EE394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C02E48-DEA9-43C0-8F1D-748B5D99AFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2398,25 +2398,47 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>40</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>60</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
